--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99691</v>
+        <v>99697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99697</v>
+        <v>99699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99339</v>
+        <v>99340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99339</v>
+        <v>99340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99339</v>
+        <v>99340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99339</v>
+        <v>99340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99699</v>
+        <v>99700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99700</v>
+        <v>99706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99706</v>
+        <v>99710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99710</v>
+        <v>99712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99712</v>
+        <v>99714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99714</v>
+        <v>99727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99727</v>
+        <v>99729</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99729</v>
+        <v>99732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99732</v>
+        <v>99742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99742</v>
+        <v>99743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136882476</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136874326</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874302</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136874314</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136875161</v>
       </c>
       <c r="B6" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136882477</v>
       </c>
       <c r="B7" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136882479</v>
       </c>
       <c r="B8" t="n">
-        <v>99743</v>
+        <v>99748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136875335</v>
       </c>
       <c r="B9" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136882478</v>
       </c>
       <c r="B10" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136882480</v>
       </c>
       <c r="B11" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136882481</v>
       </c>
       <c r="B12" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136882476</v>
+        <v>137378960</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>87465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639497</v>
+        <v>639446</v>
       </c>
       <c r="R2" t="n">
-        <v>6697422</v>
+        <v>6697453</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,54 +776,54 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136882476</t>
+          <t>https://artportalen.se/Sighting/137378960</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136874326</v>
+        <v>136882476</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rödjan, Rödjan, Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639482</v>
+        <v>639497</v>
       </c>
       <c r="R3" t="n">
-        <v>6697335</v>
+        <v>6697422</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136874326</t>
+          <t>https://artportalen.se/Sighting/136882476</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136874302</v>
+        <v>136874326</v>
       </c>
       <c r="B4" t="n">
-        <v>99388</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639464</v>
+        <v>639482</v>
       </c>
       <c r="R4" t="n">
-        <v>6697363</v>
+        <v>6697335</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,16 +980,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136874302</t>
+          <t>https://artportalen.se/Sighting/136874326</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136874314</v>
+        <v>137379242</v>
       </c>
       <c r="B5" t="n">
-        <v>99388</v>
+        <v>96624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rödjan, Rödjan, Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639470</v>
+        <v>639425</v>
       </c>
       <c r="R5" t="n">
-        <v>6697343</v>
+        <v>6697444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,51 +1082,51 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136874314</t>
+          <t>https://artportalen.se/Sighting/137379242</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136875161</v>
+        <v>137378635</v>
       </c>
       <c r="B6" t="n">
-        <v>99388</v>
+        <v>87474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>3611</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rödjan, Rödjan, Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639494</v>
+        <v>639406</v>
       </c>
       <c r="R6" t="n">
-        <v>6697329</v>
+        <v>6697437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875161</t>
+          <t>https://artportalen.se/Sighting/137378635</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136882477</v>
+        <v>137377763</v>
       </c>
       <c r="B7" t="n">
-        <v>99388</v>
+        <v>93134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639443</v>
+        <v>639434</v>
       </c>
       <c r="R7" t="n">
-        <v>6697379</v>
+        <v>6697408</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,38 +1286,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136882477</t>
+          <t>https://artportalen.se/Sighting/137377763</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136882479</v>
+        <v>137379649</v>
       </c>
       <c r="B8" t="n">
-        <v>99748</v>
+        <v>93499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639489</v>
+        <v>639414</v>
       </c>
       <c r="R8" t="n">
-        <v>6697308</v>
+        <v>6697440</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,16 +1388,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136882479</t>
+          <t>https://artportalen.se/Sighting/137379649</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136875335</v>
+        <v>137379425</v>
       </c>
       <c r="B9" t="n">
-        <v>108448</v>
+        <v>4783</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1405,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220083</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rödjan, Rödjan, Upl</t>
+          <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>639600</v>
+        <v>639408</v>
       </c>
       <c r="R9" t="n">
-        <v>6697370</v>
+        <v>6697492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1459,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1490,16 +1495,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136875335</t>
+          <t>https://artportalen.se/Sighting/137379425</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136882478</v>
+        <v>137379398</v>
       </c>
       <c r="B10" t="n">
-        <v>111404</v>
+        <v>5188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220240</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1536,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>639495</v>
+        <v>639409</v>
       </c>
       <c r="R10" t="n">
-        <v>6697405</v>
+        <v>6697491</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1566,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,51 +1602,52 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136882478</t>
+          <t>https://artportalen.se/Sighting/137379398</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136882480</v>
+        <v>137377366</v>
       </c>
       <c r="B11" t="n">
-        <v>99410</v>
+        <v>58195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hästhagen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>639500</v>
+        <v>639530</v>
       </c>
       <c r="R11" t="n">
-        <v>6697423</v>
+        <v>6697381</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1663,12 +1674,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,16 +1705,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136882480</t>
+          <t>https://artportalen.se/Sighting/137377366</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136882481</v>
+        <v>137379416</v>
       </c>
       <c r="B12" t="n">
-        <v>101625</v>
+        <v>5208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1722,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1746,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>639440</v>
+        <v>639408</v>
       </c>
       <c r="R12" t="n">
-        <v>6697389</v>
+        <v>6697492</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1776,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,6 +1811,1128 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137379416</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136874302</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rödjan, Rödjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>639464</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6697363</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136874302</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136874314</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rödjan, Rödjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>639470</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6697343</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136874314</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136875161</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rödjan, Rödjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>639494</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6697329</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875161</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136882477</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>639443</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6697379</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136882477</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136882479</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99751</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>639489</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6697308</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136882479</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136875335</v>
+      </c>
+      <c r="B18" t="n">
+        <v>108451</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Rödjan, Rödjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>639600</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6697370</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136875335</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137379234</v>
+      </c>
+      <c r="B19" t="n">
+        <v>108451</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hästhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>639425</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6697444</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137379234</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136882478</v>
+      </c>
+      <c r="B20" t="n">
+        <v>111407</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hästhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>639495</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6697405</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136882478</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137378646</v>
+      </c>
+      <c r="B21" t="n">
+        <v>111407</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hästhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>639440</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6697460</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137378646</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136882480</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hästhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>639500</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6697423</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136882480</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136882481</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hästhagen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>639440</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6697389</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tolfta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136882481</t>
         </is>
@@ -1813,6 +2951,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137378960</v>
       </c>
       <c r="B2" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136882476</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874326</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137379242</v>
       </c>
       <c r="B5" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137378635</v>
       </c>
       <c r="B6" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137377763</v>
       </c>
       <c r="B7" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137379649</v>
       </c>
       <c r="B8" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137377366</v>
       </c>
       <c r="B11" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136874302</v>
       </c>
       <c r="B13" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136874314</v>
       </c>
       <c r="B14" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136875161</v>
       </c>
       <c r="B15" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>136882477</v>
       </c>
       <c r="B16" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136882479</v>
       </c>
       <c r="B17" t="n">
-        <v>99751</v>
+        <v>99757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>136875335</v>
       </c>
       <c r="B18" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>137379234</v>
       </c>
       <c r="B19" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136882478</v>
       </c>
       <c r="B20" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137378646</v>
       </c>
       <c r="B21" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>136882480</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>136882481</v>
       </c>
       <c r="B23" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -2331,7 +2331,7 @@
         <v>136875335</v>
       </c>
       <c r="B18" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>137379234</v>
       </c>
       <c r="B19" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136882478</v>
       </c>
       <c r="B20" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137378646</v>
       </c>
       <c r="B21" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137378960</v>
       </c>
       <c r="B2" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136882476</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874326</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137379242</v>
       </c>
       <c r="B5" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137378635</v>
       </c>
       <c r="B6" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137377763</v>
       </c>
       <c r="B7" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137379649</v>
       </c>
       <c r="B8" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136874302</v>
       </c>
       <c r="B13" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136874314</v>
       </c>
       <c r="B14" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136875161</v>
       </c>
       <c r="B15" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>136882477</v>
       </c>
       <c r="B16" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136882479</v>
       </c>
       <c r="B17" t="n">
-        <v>99757</v>
+        <v>99769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>136875335</v>
       </c>
       <c r="B18" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>137379234</v>
       </c>
       <c r="B19" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136882478</v>
       </c>
       <c r="B20" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137378646</v>
       </c>
       <c r="B21" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>136882480</v>
       </c>
       <c r="B22" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>136882481</v>
       </c>
       <c r="B23" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137378960</v>
       </c>
       <c r="B2" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136882476</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136874326</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137379242</v>
       </c>
       <c r="B5" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137378635</v>
       </c>
       <c r="B6" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137377763</v>
       </c>
       <c r="B7" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137379649</v>
       </c>
       <c r="B8" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136874302</v>
       </c>
       <c r="B13" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>136874314</v>
       </c>
       <c r="B14" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>136875161</v>
       </c>
       <c r="B15" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>136882477</v>
       </c>
       <c r="B16" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>136882479</v>
       </c>
       <c r="B17" t="n">
-        <v>99769</v>
+        <v>99770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>136875335</v>
       </c>
       <c r="B18" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>137379234</v>
       </c>
       <c r="B19" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>136882478</v>
       </c>
       <c r="B20" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137378646</v>
       </c>
       <c r="B21" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>136882480</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>136882481</v>
       </c>
       <c r="B23" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137378960</v>
       </c>
       <c r="B2" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137379242</v>
       </c>
       <c r="B5" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137378635</v>
       </c>
       <c r="B6" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137377763</v>
       </c>
       <c r="B7" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137379649</v>
       </c>
       <c r="B8" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>137379234</v>
       </c>
       <c r="B19" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137378646</v>
       </c>
       <c r="B21" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 2534-2022 artfynd.xlsx
+++ b/artfynd/A 2534-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137378960</v>
       </c>
       <c r="B2" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137379242</v>
       </c>
       <c r="B5" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137378635</v>
       </c>
       <c r="B6" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137377763</v>
       </c>
       <c r="B7" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137379649</v>
       </c>
       <c r="B8" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137377366</v>
       </c>
       <c r="B11" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>137379234</v>
       </c>
       <c r="B19" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137378646</v>
       </c>
       <c r="B21" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
